--- a/artfynd/A 38578-2019 artfynd.xlsx
+++ b/artfynd/A 38578-2019 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 38578-2019 artfynd.xlsx
+++ b/artfynd/A 38578-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124097493</v>
+        <v>124384427</v>
       </c>
       <c r="B2" t="n">
         <v>57460</v>
@@ -757,22 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 38578-2019 artfynd.xlsx
+++ b/artfynd/A 38578-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124384427</v>
+        <v>124097493</v>
       </c>
       <c r="B2" t="n">
         <v>57460</v>
@@ -757,22 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 38578-2019 artfynd.xlsx
+++ b/artfynd/A 38578-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124384427</v>
       </c>
       <c r="B2" t="n">
-        <v>57460</v>
+        <v>57477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
